--- a/artfynd/A 38116-2024 artfynd.xlsx
+++ b/artfynd/A 38116-2024 artfynd.xlsx
@@ -7807,7 +7807,7 @@
         <v>136237597</v>
       </c>
       <c r="B65" t="n">
-        <v>58162</v>
+        <v>58164</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
